--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -373,7 +373,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -661,7 +661,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|Appointment|AppointmentResponse|Task)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
 </t>
   </si>
   <si>
@@ -743,7 +743,7 @@
     <t>ImagingStudy.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1181,7 +1181,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1202,7 +1202,7 @@
     <t>適用される部位の側性を示すコード（左側、右側など）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality</t>
+    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality|4.0.1</t>
   </si>
   <si>
     <t>(0020,0060)</t>
@@ -1211,7 +1211,7 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1291,13 +1291,13 @@
     <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/series-performer-function|4.0.1</t>
   </si>
   <si>
     <t>ImagingStudy.series.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1758,7 +1758,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.44140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
